--- a/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_2_1.xlsx
+++ b/fuction_ensemble_1/redes-ensemble-s/Teste02 copy/content/results/metrics_2_1.xlsx
@@ -513,826 +513,826 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_8</t>
+          <t>model_2_1_5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8295423164928434</v>
+        <v>0.7868012276490217</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4844468558613273</v>
+        <v>0.35095166544059</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7228856726215289</v>
+        <v>0.6229257788066869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6621563421153774</v>
+        <v>0.7927459744689739</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7111885585587687</v>
+        <v>0.7099557950163705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1011910443183701</v>
+        <v>0.1265640009749645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3060546170969241</v>
+        <v>0.3853031288226331</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2044507939880744</v>
+        <v>0.2853996964495853</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1701940766753076</v>
+        <v>0.1623948574408532</v>
       </c>
       <c r="K2" t="n">
-        <v>0.187322435331691</v>
+        <v>0.2238972769452193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2199711767569407</v>
+        <v>0.17691607293234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3181053981283093</v>
+        <v>0.3557583463180652</v>
       </c>
       <c r="N2" t="n">
-        <v>0.545446177314249</v>
+        <v>0.4314699403973913</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3316478034955845</v>
+        <v>0.3709037156421263</v>
       </c>
       <c r="P2" t="n">
-        <v>34.58149004184488</v>
+        <v>34.13401432439266</v>
       </c>
       <c r="Q2" t="n">
-        <v>52.86462741486789</v>
+        <v>52.41715169741567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_6</t>
+          <t>model_2_1_4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8253818396737066</v>
+        <v>0.7903316317590031</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4748052782923872</v>
+        <v>0.3445089299889461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7077034697128164</v>
+        <v>0.6169885436560428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6702087350548963</v>
+        <v>0.8235952431187441</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7056807672548866</v>
+        <v>0.7227017783852904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1036608830814503</v>
+        <v>0.1244682005897627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3117782740363114</v>
+        <v>0.3891278148984089</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2156519955590599</v>
+        <v>0.2898934672101035</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1661375565975022</v>
+        <v>0.138222769242817</v>
       </c>
       <c r="K3" t="n">
-        <v>0.190894776078281</v>
+        <v>0.2140581182264602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2188229580663765</v>
+        <v>0.1767170309866333</v>
       </c>
       <c r="M3" t="n">
-        <v>0.321964102162726</v>
+        <v>0.352800511039543</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5343515724632176</v>
+        <v>0.4408843513573417</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3356707805493648</v>
+        <v>0.3678199591922343</v>
       </c>
       <c r="P3" t="n">
-        <v>34.53326089447687</v>
+        <v>34.16741002530307</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.81639826749988</v>
+        <v>52.45054739832608</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_1</t>
+          <t>model_2_1_3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8349050594648829</v>
+        <v>0.7721261141579414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4712130484650957</v>
+        <v>0.3384488051101124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7251120124665686</v>
+        <v>0.5850296447925166</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7875228214421369</v>
+        <v>0.8099708611451163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.761140866359145</v>
+        <v>0.7001194579729804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09800748843173335</v>
+        <v>0.1352757822751642</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3139107768380403</v>
+        <v>0.3927253668102484</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2028082338457978</v>
+        <v>0.3140824982333548</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1070387333764301</v>
+        <v>0.1488982172234199</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1549234836111139</v>
+        <v>0.2314903577283873</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1945496200321155</v>
+        <v>0.1840014672399268</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3130614770803545</v>
+        <v>0.3677985620895821</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5597468252396878</v>
+        <v>0.3923363044211772</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3263891522862623</v>
+        <v>0.3834565083257191</v>
       </c>
       <c r="P4" t="n">
-        <v>34.6454227813243</v>
+        <v>34.00087950523819</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.92856015434731</v>
+        <v>52.2840168782612</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_4</t>
+          <t>model_2_1_2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8250325502475779</v>
+        <v>0.7333152821314644</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4707713500947718</v>
+        <v>0.3131190558654727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7071032986813768</v>
+        <v>0.5374282305235811</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7036799316127829</v>
+        <v>0.7868038864969217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7183379557205547</v>
+        <v>0.665025418828797</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1038682363733178</v>
+        <v>0.1583155687067284</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3141729880710406</v>
+        <v>0.4077622001500605</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2160947927434108</v>
+        <v>0.3501110263568945</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1492759128743198</v>
+        <v>0.1670508081595425</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1826853528088653</v>
+        <v>0.2585809172582185</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2143577073602947</v>
+        <v>0.1987111791157684</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3222859543531455</v>
+        <v>0.3978888899010984</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5334201339935412</v>
+        <v>0.2888407523505716</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3360063346538564</v>
+        <v>0.4148278436877373</v>
       </c>
       <c r="P5" t="n">
-        <v>34.5292642821188</v>
+        <v>33.68632993510389</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.81240165514181</v>
+        <v>51.9694673081269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_7</t>
+          <t>model_2_1_6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8216133390234084</v>
+        <v>0.7756362441924413</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4691586432446629</v>
+        <v>0.3093500884404931</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6959431857834346</v>
+        <v>0.6646582195179438</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6462757216146191</v>
+        <v>0.6602569547556896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6896976743389289</v>
+        <v>0.6631737995923646</v>
       </c>
       <c r="G6" t="n">
-        <v>0.105898027858219</v>
+        <v>0.1331920174569628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3151303605225738</v>
+        <v>0.4099996220244437</v>
       </c>
       <c r="I6" t="n">
-        <v>0.224328556636335</v>
+        <v>0.2538132732955428</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1781941899823941</v>
+        <v>0.2662072461927247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2012613733093645</v>
+        <v>0.2600102597441338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2225486113303896</v>
+        <v>0.1842623625692084</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3254197717690476</v>
+        <v>0.3649548156374468</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5243022373957558</v>
+        <v>0.4016966511798434</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3392735651650498</v>
+        <v>0.3804916976997498</v>
       </c>
       <c r="P6" t="n">
-        <v>34.49055729845578</v>
+        <v>34.03192690334689</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.77369467147879</v>
+        <v>52.3150642763699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_0</t>
+          <t>model_2_1_7</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8368706144096966</v>
+        <v>0.7749331605967911</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4684375435466552</v>
+        <v>0.3073386862687787</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7276087275192777</v>
+        <v>0.6646568798039705</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8148861376296621</v>
+        <v>0.656602295172193</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7731874258658116</v>
+        <v>0.661318323474905</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09684065010893939</v>
+        <v>0.1336093982509707</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3155584364531961</v>
+        <v>0.411193677241623</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2009661949309669</v>
+        <v>0.253814287297402</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09325403082356823</v>
+        <v>0.2690708717388925</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1471101128772676</v>
+        <v>0.2614425795181473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.187054748028514</v>
+        <v>0.1843389149944781</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3111923040644473</v>
+        <v>0.3655261936591832</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5649883050925242</v>
+        <v>0.3998217615914429</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3244404047053463</v>
+        <v>0.381087400466787</v>
       </c>
       <c r="P7" t="n">
-        <v>34.66937686741487</v>
+        <v>34.02566934832774</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.95251424043788</v>
+        <v>52.30880672135075</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_5</t>
+          <t>model_2_1_8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8199289191654577</v>
+        <v>0.7740105685567662</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4617217387999627</v>
+        <v>0.3063316070444506</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6892331907700006</v>
+        <v>0.66387135496361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6725371355795846</v>
+        <v>0.6527230135601628</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6960799574546706</v>
+        <v>0.6589644049432595</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1068979722490477</v>
+        <v>0.1341570887398305</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3195452282584922</v>
+        <v>0.4117915229727415</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2292790903064291</v>
+        <v>0.2544088348384218</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1649645880714363</v>
+        <v>0.2721105009221833</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1971218391889327</v>
+        <v>0.2632596678803025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2194955692479057</v>
+        <v>0.184179568987852</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3269525535135758</v>
+        <v>0.3662746083744142</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5198104511078874</v>
+        <v>0.3973615161513766</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3408716006017383</v>
+        <v>0.3818676767458775</v>
       </c>
       <c r="P8" t="n">
-        <v>34.47176085960451</v>
+        <v>34.0174877232289</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.75489823262752</v>
+        <v>52.30062509625191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_2</t>
+          <t>model_2_1_9</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8267086688573146</v>
+        <v>0.7738441733500487</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4596914009868807</v>
+        <v>0.3026720223948539</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7047420185546772</v>
+        <v>0.6641219899763597</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7480594727508931</v>
+        <v>0.6513515962921963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7342297617031623</v>
+        <v>0.658391253056539</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1028732199620242</v>
+        <v>0.1342558681224366</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3207505244903645</v>
+        <v>0.4139640105065676</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2178369098013738</v>
+        <v>0.2542191343695538</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1269190183433768</v>
+        <v>0.2731850813128547</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1723779640723753</v>
+        <v>0.2637021078412042</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2066264619998468</v>
+        <v>0.1844087976135916</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3207385539064866</v>
+        <v>0.3664094269017059</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5378897836195058</v>
+        <v>0.39691779560013</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3343930581666227</v>
+        <v>0.3820082347769889</v>
       </c>
       <c r="P9" t="n">
-        <v>34.54851584611077</v>
+        <v>34.01601567227845</v>
       </c>
       <c r="Q9" t="n">
-        <v>52.83165321913378</v>
+        <v>52.29915304530146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_3</t>
+          <t>model_2_1_10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8126750577432315</v>
+        <v>0.7733249059498374</v>
       </c>
       <c r="C10" t="n">
-        <v>0.434013069647382</v>
+        <v>0.3007193787166209</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6549649057637305</v>
+        <v>0.6635397968440184</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6976573752272666</v>
+        <v>0.6492290872011435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6863451793275365</v>
+        <v>0.6570286169342363</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1112041777397787</v>
+        <v>0.1345641276823857</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3359942912196472</v>
+        <v>0.4151231841437815</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2545617169552231</v>
+        <v>0.2546597843368718</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1523098707401442</v>
+        <v>0.2748481832013477</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2034357938476836</v>
+        <v>0.2647539837691097</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2168844281017746</v>
+        <v>0.1843783664815649</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3334729040563546</v>
+        <v>0.3668298347768154</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5004668206486172</v>
+        <v>0.3955330825328998</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3476695359661095</v>
+        <v>0.3824465402857061</v>
       </c>
       <c r="P10" t="n">
-        <v>34.39277465653809</v>
+        <v>34.01142881564761</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.6759120295611</v>
+        <v>52.29456618867062</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_9</t>
+          <t>model_2_1_11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5947233257325089</v>
+        <v>0.7726166218462069</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2534585380244184</v>
+        <v>0.2983668370333145</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06855979748358387</v>
+        <v>0.6623230799661837</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1724093156616375</v>
+        <v>0.6468607559294665</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01493458738061948</v>
+        <v>0.6552301494127379</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2405897408859339</v>
+        <v>0.1349845957225809</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4431792607406884</v>
+        <v>0.4165197545115015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6872026096897104</v>
+        <v>0.2555806922326705</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5906197032495599</v>
+        <v>0.2767039002049199</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6389111564696351</v>
+        <v>0.2661422962187952</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3451560309392409</v>
+        <v>0.1842483024560166</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4904994810251423</v>
+        <v>0.367402498253048</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08073779804664305</v>
+        <v>0.3936443249232185</v>
       </c>
       <c r="O11" t="n">
-        <v>0.511381059406284</v>
+        <v>0.3830435832316986</v>
       </c>
       <c r="P11" t="n">
-        <v>32.84932423211998</v>
+        <v>34.00518922562585</v>
       </c>
       <c r="Q11" t="n">
-        <v>51.13246160514299</v>
+        <v>52.28832659864886</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_14</t>
+          <t>model_2_1_1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4992041056483132</v>
+        <v>0.7412544031856647</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1662102261068479</v>
+        <v>0.2957785641557509</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1415992611895946</v>
+        <v>0.546574141332359</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5830474149032558</v>
+        <v>0.8320383912944167</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2640654996107579</v>
+        <v>0.6924666405923303</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2972940761433715</v>
+        <v>0.1536025634967828</v>
       </c>
       <c r="H12" t="n">
-        <v>0.494973627625788</v>
+        <v>0.4180562650991898</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8422548107649542</v>
+        <v>0.3431886752072464</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7974851290673155</v>
+        <v>0.1316071011474579</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8198699699161349</v>
+        <v>0.2373978881773522</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3767975523095572</v>
+        <v>0.1979390106856866</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5452468029648331</v>
+        <v>0.391921629279098</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3354557182711648</v>
+        <v>0.3100117418284393</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5684590881835273</v>
+        <v>0.408606544427126</v>
       </c>
       <c r="P12" t="n">
-        <v>32.42606694939006</v>
+        <v>33.74677353795131</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.70920432241306</v>
+        <v>52.02991091097432</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_13</t>
+          <t>model_2_1_12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5002866578521141</v>
+        <v>0.772245562803046</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1553697120207089</v>
+        <v>0.2947470754552313</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1395486912360659</v>
+        <v>0.6624185801321352</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5780263857878294</v>
+        <v>0.6447179355284072</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2609493133581844</v>
+        <v>0.6541894397498536</v>
       </c>
       <c r="G13" t="n">
-        <v>0.296651426391375</v>
+        <v>0.1352048723995173</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5014090250731453</v>
+        <v>0.41866860134981</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8407419310120627</v>
+        <v>0.2555084101278712</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7949557063763272</v>
+        <v>0.2783829171150125</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8178488186941949</v>
+        <v>0.2669456636214418</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3764980569493998</v>
+        <v>0.1842188496042848</v>
       </c>
       <c r="M13" t="n">
-        <v>0.544657164087075</v>
+        <v>0.3677021517471951</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3325689123943623</v>
+        <v>0.3926548341414561</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5678443471580223</v>
+        <v>0.3833559935954599</v>
       </c>
       <c r="P13" t="n">
-        <v>32.4303949559162</v>
+        <v>34.00192815512935</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.71353232893921</v>
+        <v>52.28506552815236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_12</t>
+          <t>model_2_1_13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5081976897140996</v>
+        <v>0.7722329038611342</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1350971593797455</v>
+        <v>0.2896682871462993</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.124101371490184</v>
+        <v>0.6628540853590295</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5418797602035621</v>
+        <v>0.6437971015992946</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2381260483809766</v>
+        <v>0.6539356001842502</v>
       </c>
       <c r="G14" t="n">
-        <v>0.291955096139318</v>
+        <v>0.135212387294274</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5134436880494968</v>
+        <v>0.4216835894822233</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8293451302154015</v>
+        <v>0.2551787852090303</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7767462730403213</v>
+        <v>0.2791044408309538</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8030457016278614</v>
+        <v>0.2671416130199921</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3743903309119807</v>
+        <v>0.1843541138980884</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5403286926855894</v>
+        <v>0.3677123703307708</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3114728274290677</v>
+        <v>0.3926210769630245</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5633316037678044</v>
+        <v>0.3833666472052938</v>
       </c>
       <c r="P14" t="n">
-        <v>32.46231053776813</v>
+        <v>34.00181699514249</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.74544791079114</v>
+        <v>52.2849543681655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_10</t>
+          <t>model_2_1_14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5507406781293461</v>
+        <v>0.7724890160264681</v>
       </c>
       <c r="C15" t="n">
-        <v>0.129637930760877</v>
+        <v>0.2860395446994978</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03243981307767219</v>
+        <v>0.6647598023286567</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3569909677492082</v>
+        <v>0.6428532306572049</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1141916185374696</v>
+        <v>0.6543908309241953</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2666997404546189</v>
+        <v>0.1350603480494623</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5166845219840542</v>
+        <v>0.4238377677521564</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7617186073542157</v>
+        <v>0.2537363873624493</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6836056247404273</v>
+        <v>0.2798440153057583</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7226621160473214</v>
+        <v>0.2667902013341038</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3608731441695931</v>
+        <v>0.1844691031957583</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5164298020589234</v>
+        <v>0.367505575535205</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1980248583217437</v>
+        <v>0.3933040427372484</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5384152878896377</v>
+        <v>0.3831510487271565</v>
       </c>
       <c r="P15" t="n">
-        <v>32.64326364193635</v>
+        <v>34.00406715567986</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.92640101495936</v>
+        <v>52.28720452870287</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_11</t>
+          <t>model_2_1_15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5127740175941788</v>
+        <v>0.7720745794032084</v>
       </c>
       <c r="C16" t="n">
-        <v>0.109361846858849</v>
+        <v>0.2802383722781081</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1152025628640507</v>
+        <v>0.6638665594318001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5207411069203693</v>
+        <v>0.6415008522580188</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2248556205181691</v>
+        <v>0.6532665627028492</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2892383902226319</v>
+        <v>0.1353063755317592</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5287212812695162</v>
+        <v>0.4272815942990935</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8227797226943532</v>
+        <v>0.2544124644774848</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7660973427030791</v>
+        <v>0.2809036777020819</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7944385326987161</v>
+        <v>0.2676580710897833</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3732487745557917</v>
+        <v>0.1846035229842634</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5378088788990304</v>
+        <v>0.3678401494287419</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2992692864155231</v>
+        <v>0.3921988784085559</v>
       </c>
       <c r="O16" t="n">
-        <v>0.560704516291618</v>
+        <v>0.3834998661240047</v>
       </c>
       <c r="P16" t="n">
-        <v>32.48100810246575</v>
+        <v>34.00042724693745</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.76414547548876</v>
+        <v>52.28356461996046</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.7719781520914306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2759120484732871</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6644290303069801</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.6403698670511309</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6529683109002571</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1353636189494735</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4298498869970926</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2539867418796098</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2817898664309603</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.267888304155285</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1847404468202115</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3679179513824699</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3919417389104817</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.3835809802679752</v>
       </c>
       <c r="P17" t="n">
-        <v>32.41040644971245</v>
+        <v>33.99958129548756</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.69354382273546</v>
+        <v>52.28271866851057</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.7721010717116953</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2737191378080046</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6662668040953423</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.6390524535446849</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6532006519349143</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1352906485530332</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4311516934968125</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2525957688248045</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2828221319226524</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2677089503737284</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1848583097300819</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3678187713440319</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3922695245645208</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.3834775779299698</v>
       </c>
       <c r="P18" t="n">
-        <v>32.41040644971245</v>
+        <v>34.00065972515921</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.69354382273546</v>
+        <v>52.28379709818222</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.7719760182467972</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2720837549104055</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6668980788159299</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.6377678661149914</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6528581743129823</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1353648856918251</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4321225274296902</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2521179700162256</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2838286763889463</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2679733232025859</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1849481770115124</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3679196728795909</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3919360486581258</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.3835827750527925</v>
       </c>
       <c r="P19" t="n">
-        <v>32.41040644971245</v>
+        <v>33.99956257943322</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.69354382273546</v>
+        <v>52.28269995245623</v>
       </c>
     </row>
     <row r="20">
@@ -1507,107 +1507,107 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.7718850673891479</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2710264680438137</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6676301427072256</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.6365726287857161</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6526104550720868</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1354188780497983</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4327501785861135</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2515638859642946</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2847652101677152</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2681645480660049</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1850156789176834</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3679930407627273</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3916935130377277</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.3836592663586066</v>
       </c>
       <c r="P20" t="n">
-        <v>32.41040644971245</v>
+        <v>33.99876500785148</v>
       </c>
       <c r="Q20" t="n">
-        <v>50.69354382273546</v>
+        <v>52.28190238087449</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_20</t>
+          <t>model_2_1_22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.769656928998822</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2667100227756311</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6665517628198467</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.626563435836178</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6470019026861622</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1367415972488625</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4353126069580335</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2523800894468379</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2926079599428935</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2724940246948657</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1853819710421395</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3697858802724389</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3857518106635254</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.385528430757936</v>
       </c>
       <c r="P21" t="n">
-        <v>32.41040644971245</v>
+        <v>33.97932457129144</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.69354382273546</v>
+        <v>52.26246194431445</v>
       </c>
     </row>
     <row r="22">
@@ -1617,107 +1617,107 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.769656928998822</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2667100227756311</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6665517628198467</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.626563435836178</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6470019026861622</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1367415972488625</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4353126069580335</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2523800894468379</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2926079599428935</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2724940246948657</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1853819710421395</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3697858802724389</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3857518106635254</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.385528430757936</v>
       </c>
       <c r="P22" t="n">
-        <v>32.41040644971245</v>
+        <v>33.97932457129144</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.69354382273546</v>
+        <v>52.26246194431445</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_22</t>
+          <t>model_2_1_24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.769656928998822</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2667100227756311</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6665517628198467</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.626563435836178</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6470019026861622</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1367415972488625</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4353126069580335</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2523800894468379</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2926079599428935</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2724940246948657</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1853819710421395</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3697858802724389</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3857518106635254</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.385528430757936</v>
       </c>
       <c r="P23" t="n">
-        <v>32.41040644971245</v>
+        <v>33.97932457129144</v>
       </c>
       <c r="Q23" t="n">
-        <v>50.69354382273546</v>
+        <v>52.26246194431445</v>
       </c>
     </row>
     <row r="24">
@@ -1727,162 +1727,162 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.769656928998822</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2667100227756311</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6665517628198467</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.626563435836178</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6470019026861622</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1367415972488625</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4353126069580335</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2523800894468379</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2926079599428935</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2724940246948657</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1853819710421395</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3697858802724389</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3857518106635254</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.385528430757936</v>
       </c>
       <c r="P24" t="n">
-        <v>32.41040644971245</v>
+        <v>33.97932457129144</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.69354382273546</v>
+        <v>52.26246194431445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_24</t>
+          <t>model_2_1_20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4952673559247619</v>
+        <v>0.769656928998822</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08659052287161872</v>
+        <v>0.2667100227756311</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1494439937320495</v>
+        <v>0.6665517628198467</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.60067215082878</v>
+        <v>0.626563435836178</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2753717878463877</v>
+        <v>0.6470019026861622</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2996311008380048</v>
+        <v>0.1367415972488625</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5422393228583134</v>
+        <v>0.4353126069580335</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8480425367627462</v>
+        <v>0.2523800894468379</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8063638680564461</v>
+        <v>0.2926079599428935</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8272032024095961</v>
+        <v>0.2724940246948657</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3780250853602565</v>
+        <v>0.1853819710421395</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5473856965961065</v>
+        <v>0.3697858802724389</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3459537175339682</v>
+        <v>0.3857518106635254</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5706890389448043</v>
+        <v>0.385528430757936</v>
       </c>
       <c r="P25" t="n">
-        <v>32.41040644971245</v>
+        <v>33.97932457129144</v>
       </c>
       <c r="Q25" t="n">
-        <v>50.69354382273546</v>
+        <v>52.26246194431445</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_2_1_15</t>
+          <t>model_2_1_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4956197932927938</v>
+        <v>0.7227128650169201</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0863774893089444</v>
+        <v>0.2082224726815601</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1486823917478424</v>
+        <v>0.5516331620022884</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5991813465473199</v>
+        <v>0.8773867511622255</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2743596699162001</v>
+        <v>0.7179620740103627</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2994218787918395</v>
+        <v>0.1646096215064935</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5423657887836877</v>
+        <v>0.4700333432244837</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8474806382429291</v>
+        <v>0.3393596068637231</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8056128518622236</v>
+        <v>0.09607418246450145</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8265467450525763</v>
+        <v>0.2177168946641123</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3779208324664454</v>
+        <v>0.2064918047581042</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5471945529625084</v>
+        <v>0.4057211129661525</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3450138845525497</v>
+        <v>0.2605676400451203</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5704897579310021</v>
+        <v>0.4229935007036077</v>
       </c>
       <c r="P26" t="n">
-        <v>32.41180346841889</v>
+        <v>33.60835707716124</v>
       </c>
       <c r="Q26" t="n">
-        <v>50.6949408414419</v>
+        <v>51.89149445018425</v>
       </c>
     </row>
   </sheetData>
